--- a/final/soccer/static/data/Squad Wages.xlsx
+++ b/final/soccer/static/data/Squad Wages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정지원\OneDrive\바탕 화면\北京大学\3학년 2학기\数据可视化\作业\小组作业\数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\Data-Visualization\final\soccer\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{851AA346-97C2-4F1F-A0E7-8F6D583AB626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96706C0C-8B20-4D06-9ADE-26594C35BB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11610" yWindow="2160" windowWidth="17100" windowHeight="11295" xr2:uid="{854615C1-8956-4313-BA23-1863955D2AA1}"/>
+    <workbookView minimized="1" xWindow="2860" yWindow="3140" windowWidth="17280" windowHeight="8880" xr2:uid="{854615C1-8956-4313-BA23-1863955D2AA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,11 +669,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -702,14 +702,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -911,7 +911,7 @@
     <xf numFmtId="9" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -931,8 +931,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2193,7 +2193,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2490,9 +2490,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4310F26D-7765-4564-887B-946EBD28BBB1}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="36.109375" customWidth="1"/>
+    <col min="5" max="5" width="41.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" thickBot="1">
+    <row r="1" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2512,7 +2517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -2532,7 +2537,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2552,7 +2557,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2572,7 +2577,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2592,7 +2597,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2612,7 +2617,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -2632,7 +2637,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -2652,7 +2657,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -2672,7 +2677,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -2692,7 +2697,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -2712,7 +2717,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -2732,7 +2737,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -2752,7 +2757,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -2772,7 +2777,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -2792,7 +2797,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -2812,7 +2817,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -2832,7 +2837,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -2852,7 +2857,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -2872,7 +2877,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>19</v>
       </c>
@@ -2892,7 +2897,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>20</v>
       </c>

--- a/final/soccer/static/data/Squad Wages.xlsx
+++ b/final/soccer/static/data/Squad Wages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\Data-Visualization\final\soccer\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96706C0C-8B20-4D06-9ADE-26594C35BB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5CCB0E-F831-4D9C-9B35-92122B85D1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2860" yWindow="3140" windowWidth="17280" windowHeight="8880" xr2:uid="{854615C1-8956-4313-BA23-1863955D2AA1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{854615C1-8956-4313-BA23-1863955D2AA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2490,14 +2490,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4310F26D-7765-4564-887B-946EBD28BBB1}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="36.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.9140625" customWidth="1"/>
+    <col min="4" max="4" width="36.08203125" customWidth="1"/>
     <col min="5" max="5" width="41.33203125" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2517,7 +2518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -2537,7 +2538,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2557,7 +2558,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2577,7 +2578,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2597,7 +2598,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2617,7 +2618,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -2637,7 +2638,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -2657,7 +2658,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -2677,7 +2678,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -2697,7 +2698,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -2717,7 +2718,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -2737,7 +2738,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -2757,7 +2758,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -2777,7 +2778,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -2797,7 +2798,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -2837,7 +2838,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -2857,7 +2858,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -2877,7 +2878,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>19</v>
       </c>
@@ -2897,7 +2898,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>20</v>
       </c>
